--- a/data/nzd0500/nzd0500.xlsx
+++ b/data/nzd0500/nzd0500.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M523"/>
+  <dimension ref="A1:M524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23983,6 +23983,51 @@
         <v>372.79</v>
       </c>
       <c r="M523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="C524" t="n">
+        <v>360.17</v>
+      </c>
+      <c r="D524" t="n">
+        <v>357.06</v>
+      </c>
+      <c r="E524" t="n">
+        <v>356.19</v>
+      </c>
+      <c r="F524" t="n">
+        <v>354.63</v>
+      </c>
+      <c r="G524" t="n">
+        <v>355.73</v>
+      </c>
+      <c r="H524" t="n">
+        <v>357.62</v>
+      </c>
+      <c r="I524" t="n">
+        <v>359.85</v>
+      </c>
+      <c r="J524" t="n">
+        <v>363.09</v>
+      </c>
+      <c r="K524" t="n">
+        <v>364.78</v>
+      </c>
+      <c r="L524" t="n">
+        <v>372.09</v>
+      </c>
+      <c r="M524" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23999,7 +24044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B616"/>
+  <dimension ref="A1:B617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30162,6 +30207,16 @@
       </c>
       <c r="B616" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -30330,28 +30385,28 @@
         <v>0.0761</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3419737531871182</v>
+        <v>-0.3445028303906465</v>
       </c>
       <c r="J2" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K2" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1090645096307582</v>
+        <v>0.110696285913999</v>
       </c>
       <c r="M2" t="n">
-        <v>5.245500617514423</v>
+        <v>5.250672221753305</v>
       </c>
       <c r="N2" t="n">
-        <v>45.85188339871747</v>
+        <v>45.84630406420854</v>
       </c>
       <c r="O2" t="n">
-        <v>6.771401878393976</v>
+        <v>6.770989888059835</v>
       </c>
       <c r="P2" t="n">
-        <v>373.7121067051208</v>
+        <v>373.7415360794161</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30408,28 +30463,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3046532627060103</v>
+        <v>-0.3067751041884215</v>
       </c>
       <c r="J3" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K3" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0886949525466596</v>
+        <v>0.09002595991029183</v>
       </c>
       <c r="M3" t="n">
-        <v>5.28807236663418</v>
+        <v>5.288611571801385</v>
       </c>
       <c r="N3" t="n">
-        <v>45.77046857793923</v>
+        <v>45.74073636514197</v>
       </c>
       <c r="O3" t="n">
-        <v>6.765387540853756</v>
+        <v>6.763189806972888</v>
       </c>
       <c r="P3" t="n">
-        <v>373.686664958333</v>
+        <v>373.7113555716106</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30486,28 +30541,28 @@
         <v>0.1015</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3508108149043695</v>
+        <v>-0.3526611326078626</v>
       </c>
       <c r="J4" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K4" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1243632810387489</v>
+        <v>0.1258081506975096</v>
       </c>
       <c r="M4" t="n">
-        <v>4.854451692159159</v>
+        <v>4.854252006711364</v>
       </c>
       <c r="N4" t="n">
-        <v>41.58977414379342</v>
+        <v>41.55419328995657</v>
       </c>
       <c r="O4" t="n">
-        <v>6.449013424066771</v>
+        <v>6.446254206122853</v>
       </c>
       <c r="P4" t="n">
-        <v>371.0884966748274</v>
+        <v>371.1100277266218</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30564,28 +30619,28 @@
         <v>0.0692</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3729419472271471</v>
+        <v>-0.3747905533306084</v>
       </c>
       <c r="J5" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K5" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1655394662318037</v>
+        <v>0.1672488316462636</v>
       </c>
       <c r="M5" t="n">
-        <v>4.381179886388978</v>
+        <v>4.38143892805116</v>
       </c>
       <c r="N5" t="n">
-        <v>33.65081138020813</v>
+        <v>33.63032893211886</v>
       </c>
       <c r="O5" t="n">
-        <v>5.800931940663339</v>
+        <v>5.799166227322584</v>
       </c>
       <c r="P5" t="n">
-        <v>370.7998479988289</v>
+        <v>370.821359133747</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30642,28 +30697,28 @@
         <v>0.0794</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.360025526484623</v>
+        <v>-0.3617078524970547</v>
       </c>
       <c r="J6" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K6" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1490779391733629</v>
+        <v>0.1506115892696666</v>
       </c>
       <c r="M6" t="n">
-        <v>4.593422006425199</v>
+        <v>4.591445996901007</v>
       </c>
       <c r="N6" t="n">
-        <v>35.51009321901551</v>
+        <v>35.4785203786025</v>
       </c>
       <c r="O6" t="n">
-        <v>5.95903458783514</v>
+        <v>5.95638484137841</v>
       </c>
       <c r="P6" t="n">
-        <v>368.4625219234472</v>
+        <v>368.4820981553779</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30720,28 +30775,28 @@
         <v>0.134</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3149683996197305</v>
+        <v>-0.3157428077516334</v>
       </c>
       <c r="J7" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K7" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1251054010340352</v>
+        <v>0.1260298379463657</v>
       </c>
       <c r="M7" t="n">
-        <v>4.622746630906405</v>
+        <v>4.617643175069823</v>
       </c>
       <c r="N7" t="n">
-        <v>33.29833091585449</v>
+        <v>33.24235984998557</v>
       </c>
       <c r="O7" t="n">
-        <v>5.770470597434363</v>
+        <v>5.76561877425013</v>
       </c>
       <c r="P7" t="n">
-        <v>366.0171320280789</v>
+        <v>366.0261433570883</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30798,28 +30853,28 @@
         <v>0.1151</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.337546829711901</v>
+        <v>-0.3375866600342182</v>
       </c>
       <c r="J8" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K8" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1409105868057061</v>
+        <v>0.1413924529282883</v>
       </c>
       <c r="M8" t="n">
-        <v>4.58900969522604</v>
+        <v>4.580420922438004</v>
       </c>
       <c r="N8" t="n">
-        <v>33.34046339978727</v>
+        <v>33.27673526494028</v>
       </c>
       <c r="O8" t="n">
-        <v>5.774120140747616</v>
+        <v>5.768599072993397</v>
       </c>
       <c r="P8" t="n">
-        <v>366.5964639983015</v>
+        <v>366.5969274801842</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30876,28 +30931,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2124616450442845</v>
+        <v>-0.2125704190465568</v>
       </c>
       <c r="J9" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K9" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06145802323640526</v>
+        <v>0.06173307676824247</v>
       </c>
       <c r="M9" t="n">
-        <v>4.602267296909542</v>
+        <v>4.594118155053228</v>
       </c>
       <c r="N9" t="n">
-        <v>33.08605711426676</v>
+        <v>33.02294690820554</v>
       </c>
       <c r="O9" t="n">
-        <v>5.752048079968278</v>
+        <v>5.746559571448428</v>
       </c>
       <c r="P9" t="n">
-        <v>365.7179307286027</v>
+        <v>365.7191964672768</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30954,28 +31009,28 @@
         <v>0.1027</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08383695319458453</v>
+        <v>-0.08356775946732534</v>
       </c>
       <c r="J10" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K10" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009919767731742302</v>
+        <v>0.00989308592986804</v>
       </c>
       <c r="M10" t="n">
-        <v>4.64061804447246</v>
+        <v>4.633063853485835</v>
       </c>
       <c r="N10" t="n">
-        <v>33.67043142353127</v>
+        <v>33.60698205918681</v>
       </c>
       <c r="O10" t="n">
-        <v>5.802622805553646</v>
+        <v>5.797152927013985</v>
       </c>
       <c r="P10" t="n">
-        <v>364.596462400052</v>
+        <v>364.5933299520008</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31032,28 +31087,28 @@
         <v>0.0915</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03121241006002041</v>
+        <v>0.03087691040604969</v>
       </c>
       <c r="J11" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K11" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L11" t="n">
-        <v>0.00141983340519003</v>
+        <v>0.001394653572655336</v>
       </c>
       <c r="M11" t="n">
-        <v>4.569996668552301</v>
+        <v>4.563062450136356</v>
       </c>
       <c r="N11" t="n">
-        <v>32.88584271919562</v>
+        <v>32.82440811518428</v>
       </c>
       <c r="O11" t="n">
-        <v>5.734617922686359</v>
+        <v>5.729258949915275</v>
       </c>
       <c r="P11" t="n">
-        <v>364.8336670055191</v>
+        <v>364.8375710163888</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31110,28 +31165,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05479613833951001</v>
+        <v>0.05579383640576862</v>
       </c>
       <c r="J12" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K12" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004580835230505897</v>
+        <v>0.004764132292444545</v>
       </c>
       <c r="M12" t="n">
-        <v>4.56339274303547</v>
+        <v>4.55881518691379</v>
       </c>
       <c r="N12" t="n">
-        <v>31.31627191943277</v>
+        <v>31.26916911588547</v>
       </c>
       <c r="O12" t="n">
-        <v>5.596094345115419</v>
+        <v>5.591884218748227</v>
       </c>
       <c r="P12" t="n">
-        <v>368.0570069119367</v>
+        <v>368.0453972901408</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31169,7 +31224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M523"/>
+  <dimension ref="A1:M524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66213,6 +66268,73 @@
         </is>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-45.76003752398672,170.67819610125807</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-45.76030826549099,170.67898941648957</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>-45.76055570609723,170.67980197697688</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>-45.76081408798336,170.68060883405943</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>-45.76101723620642,170.68143158229253</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>-45.761164557336826,170.68229877217217</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>-45.76130706128798,170.68316786097293</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>-45.76141012874732,170.68403532709573</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>-45.761451350949066,170.6849146873586</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>-45.7614772399134,170.6857978441426</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>-45.76142503406129,170.6866924956445</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0500/nzd0500.xlsx
+++ b/data/nzd0500/nzd0500.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M524"/>
+  <dimension ref="A1:M525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24030,6 +24030,51 @@
       <c r="M524" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>352.03</v>
+      </c>
+      <c r="C525" t="n">
+        <v>354.86</v>
+      </c>
+      <c r="D525" t="n">
+        <v>352.18</v>
+      </c>
+      <c r="E525" t="n">
+        <v>353.22</v>
+      </c>
+      <c r="F525" t="n">
+        <v>349.81</v>
+      </c>
+      <c r="G525" t="n">
+        <v>350.85</v>
+      </c>
+      <c r="H525" t="n">
+        <v>352.64</v>
+      </c>
+      <c r="I525" t="n">
+        <v>355.02</v>
+      </c>
+      <c r="J525" t="n">
+        <v>357.89</v>
+      </c>
+      <c r="K525" t="n">
+        <v>360.07</v>
+      </c>
+      <c r="L525" t="n">
+        <v>368.39</v>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -24044,7 +24089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B617"/>
+  <dimension ref="A1:B618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30217,6 +30262,16 @@
       </c>
       <c r="B617" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>-0.11</v>
       </c>
     </row>
   </sheetData>
@@ -30385,28 +30440,28 @@
         <v>0.0761</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3445028303906465</v>
+        <v>-0.3493789607861045</v>
       </c>
       <c r="J2" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K2" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L2" t="n">
-        <v>0.110696285913999</v>
+        <v>0.113210788109622</v>
       </c>
       <c r="M2" t="n">
-        <v>5.250672221753305</v>
+        <v>5.269667251719975</v>
       </c>
       <c r="N2" t="n">
-        <v>45.84630406420854</v>
+        <v>46.06152842330746</v>
       </c>
       <c r="O2" t="n">
-        <v>6.770989888059835</v>
+        <v>6.78686440289678</v>
       </c>
       <c r="P2" t="n">
-        <v>373.7415360794161</v>
+        <v>373.7984872850384</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30463,28 +30518,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3067751041884215</v>
+        <v>-0.3109280555248221</v>
       </c>
       <c r="J3" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K3" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09002595991029183</v>
+        <v>0.09216799815728316</v>
       </c>
       <c r="M3" t="n">
-        <v>5.288611571801385</v>
+        <v>5.299142704941423</v>
       </c>
       <c r="N3" t="n">
-        <v>45.74073636514197</v>
+        <v>45.87302869143912</v>
       </c>
       <c r="O3" t="n">
-        <v>6.763189806972888</v>
+        <v>6.772963065855233</v>
       </c>
       <c r="P3" t="n">
-        <v>373.7113555716106</v>
+        <v>373.759860342057</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30541,28 +30596,28 @@
         <v>0.1015</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3526611326078626</v>
+        <v>-0.3563776234528426</v>
       </c>
       <c r="J4" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K4" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1258081506975096</v>
+        <v>0.1280814541621599</v>
       </c>
       <c r="M4" t="n">
-        <v>4.854252006711364</v>
+        <v>4.863035190671979</v>
       </c>
       <c r="N4" t="n">
-        <v>41.55419328995657</v>
+        <v>41.65074560135088</v>
       </c>
       <c r="O4" t="n">
-        <v>6.446254206122853</v>
+        <v>6.45373888543307</v>
       </c>
       <c r="P4" t="n">
-        <v>371.1100277266218</v>
+        <v>371.1534348173146</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30619,28 +30674,28 @@
         <v>0.0692</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3747905533306084</v>
+        <v>-0.3777715822873259</v>
       </c>
       <c r="J5" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K5" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1672488316462636</v>
+        <v>0.1695252325975223</v>
       </c>
       <c r="M5" t="n">
-        <v>4.38143892805116</v>
+        <v>4.38692313680722</v>
       </c>
       <c r="N5" t="n">
-        <v>33.63032893211886</v>
+        <v>33.67928965564251</v>
       </c>
       <c r="O5" t="n">
-        <v>5.799166227322584</v>
+        <v>5.803386050888094</v>
       </c>
       <c r="P5" t="n">
-        <v>370.821359133747</v>
+        <v>370.8561763308503</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30697,28 +30752,28 @@
         <v>0.0794</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3617078524970547</v>
+        <v>-0.3652345852743584</v>
       </c>
       <c r="J6" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K6" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1506115892696666</v>
+        <v>0.1530221781910333</v>
       </c>
       <c r="M6" t="n">
-        <v>4.591445996901007</v>
+        <v>4.596877178731506</v>
       </c>
       <c r="N6" t="n">
-        <v>35.4785203786025</v>
+        <v>35.56916826242754</v>
       </c>
       <c r="O6" t="n">
-        <v>5.95638484137841</v>
+        <v>5.963989290938368</v>
       </c>
       <c r="P6" t="n">
-        <v>368.4820981553779</v>
+        <v>368.5232889495704</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30775,28 +30830,28 @@
         <v>0.134</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3157428077516334</v>
+        <v>-0.3183890877751622</v>
       </c>
       <c r="J7" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K7" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1260298379463657</v>
+        <v>0.1280019059646177</v>
       </c>
       <c r="M7" t="n">
-        <v>4.617643175069823</v>
+        <v>4.621464301039652</v>
       </c>
       <c r="N7" t="n">
-        <v>33.24235984998557</v>
+        <v>33.26807780222688</v>
       </c>
       <c r="O7" t="n">
-        <v>5.76561877425013</v>
+        <v>5.767848628581273</v>
       </c>
       <c r="P7" t="n">
-        <v>366.0261433570883</v>
+        <v>366.0570508237743</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30853,28 +30908,28 @@
         <v>0.1151</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3375866600342182</v>
+        <v>-0.3395391109307211</v>
       </c>
       <c r="J8" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K8" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1413924529282883</v>
+        <v>0.1430822422467278</v>
       </c>
       <c r="M8" t="n">
-        <v>4.580420922438004</v>
+        <v>4.580728237357711</v>
       </c>
       <c r="N8" t="n">
-        <v>33.27673526494028</v>
+        <v>33.26176413243568</v>
       </c>
       <c r="O8" t="n">
-        <v>5.768599072993397</v>
+        <v>5.767301286774923</v>
       </c>
       <c r="P8" t="n">
-        <v>366.5969274801842</v>
+        <v>366.619731306878</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30931,28 +30986,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2125704190465568</v>
+        <v>-0.2145367915736632</v>
       </c>
       <c r="J9" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K9" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06173307676824247</v>
+        <v>0.06294299870343867</v>
       </c>
       <c r="M9" t="n">
-        <v>4.594118155053228</v>
+        <v>4.597006704663483</v>
       </c>
       <c r="N9" t="n">
-        <v>33.02294690820554</v>
+        <v>33.00915470086767</v>
       </c>
       <c r="O9" t="n">
-        <v>5.746559571448428</v>
+        <v>5.745359405717598</v>
       </c>
       <c r="P9" t="n">
-        <v>365.7191964672768</v>
+        <v>365.7421628929133</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31009,28 +31064,28 @@
         <v>0.1027</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08356775946732534</v>
+        <v>-0.08530385274893434</v>
       </c>
       <c r="J10" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K10" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00989308592986804</v>
+        <v>0.01033101613842724</v>
       </c>
       <c r="M10" t="n">
-        <v>4.633063853485835</v>
+        <v>4.632948533887136</v>
       </c>
       <c r="N10" t="n">
-        <v>33.60698205918681</v>
+        <v>33.58122021460218</v>
       </c>
       <c r="O10" t="n">
-        <v>5.797152927013985</v>
+        <v>5.794930561672174</v>
       </c>
       <c r="P10" t="n">
-        <v>364.5933299520008</v>
+        <v>364.6136068103785</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31087,28 +31142,28 @@
         <v>0.0915</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03087691040604969</v>
+        <v>0.0287206380490653</v>
       </c>
       <c r="J11" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K11" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001394653572655336</v>
+        <v>0.001209270948579366</v>
       </c>
       <c r="M11" t="n">
-        <v>4.563062450136356</v>
+        <v>4.565843191579569</v>
       </c>
       <c r="N11" t="n">
-        <v>32.82440811518428</v>
+        <v>32.82096231901593</v>
       </c>
       <c r="O11" t="n">
-        <v>5.729258949915275</v>
+        <v>5.728958222837371</v>
       </c>
       <c r="P11" t="n">
-        <v>364.8375710163888</v>
+        <v>364.86275539425</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31165,28 +31220,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05579383640576862</v>
+        <v>0.05535807929620193</v>
       </c>
       <c r="J12" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K12" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004764132292444545</v>
+        <v>0.004707654344578094</v>
       </c>
       <c r="M12" t="n">
-        <v>4.55881518691379</v>
+        <v>4.552609843906516</v>
       </c>
       <c r="N12" t="n">
-        <v>31.26916911588547</v>
+        <v>31.21191267972418</v>
       </c>
       <c r="O12" t="n">
-        <v>5.591884218748227</v>
+        <v>5.586762271631413</v>
       </c>
       <c r="P12" t="n">
-        <v>368.0453972901408</v>
+        <v>368.0504867546825</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31224,7 +31279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M524"/>
+  <dimension ref="A1:M525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66335,6 +66390,73 @@
         </is>
       </c>
     </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-45.760085696566826,170.6781579993471</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-45.76035135118554,170.67895992744315</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-45.76059592113751,170.67977680288288</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>-45.76083881478145,170.68059436113202</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>-45.76105857133008,170.68141284354235</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>-45.761206788380996,170.6822816115053</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>-45.76135046612169,170.6831519791365</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>-45.76145288782076,170.68402425132</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>-45.76149784409633,170.68490723160988</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>-45.761519527508305,170.68579392397714</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>-45.761458294004285,170.6866904945622</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0500/nzd0500.xlsx
+++ b/data/nzd0500/nzd0500.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M525"/>
+  <dimension ref="A1:M527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24075,6 +24075,96 @@
       <c r="M525" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>347.62</v>
+      </c>
+      <c r="C526" t="n">
+        <v>352.22</v>
+      </c>
+      <c r="D526" t="n">
+        <v>348.48</v>
+      </c>
+      <c r="E526" t="n">
+        <v>351.68</v>
+      </c>
+      <c r="F526" t="n">
+        <v>348.14</v>
+      </c>
+      <c r="G526" t="n">
+        <v>349.31</v>
+      </c>
+      <c r="H526" t="n">
+        <v>349.77</v>
+      </c>
+      <c r="I526" t="n">
+        <v>352.83</v>
+      </c>
+      <c r="J526" t="n">
+        <v>354.29</v>
+      </c>
+      <c r="K526" t="n">
+        <v>357.32</v>
+      </c>
+      <c r="L526" t="n">
+        <v>364.98</v>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>346.71</v>
+      </c>
+      <c r="C527" t="n">
+        <v>352.04</v>
+      </c>
+      <c r="D527" t="n">
+        <v>348</v>
+      </c>
+      <c r="E527" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="F527" t="n">
+        <v>346.92</v>
+      </c>
+      <c r="G527" t="n">
+        <v>349.26</v>
+      </c>
+      <c r="H527" t="n">
+        <v>348.93</v>
+      </c>
+      <c r="I527" t="n">
+        <v>351.93</v>
+      </c>
+      <c r="J527" t="n">
+        <v>353.52</v>
+      </c>
+      <c r="K527" t="n">
+        <v>356.8</v>
+      </c>
+      <c r="L527" t="n">
+        <v>362.94</v>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -24089,7 +24179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B618"/>
+  <dimension ref="A1:B620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30272,6 +30362,26 @@
       </c>
       <c r="B618" t="n">
         <v>-0.11</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>-0.88</v>
       </c>
     </row>
   </sheetData>
@@ -30440,28 +30550,28 @@
         <v>0.0761</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3493789607861045</v>
+        <v>-0.3628810790515301</v>
       </c>
       <c r="J2" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K2" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L2" t="n">
-        <v>0.113210788109622</v>
+        <v>0.1192918267770201</v>
       </c>
       <c r="M2" t="n">
-        <v>5.269667251719975</v>
+        <v>5.330378007497241</v>
       </c>
       <c r="N2" t="n">
-        <v>46.06152842330746</v>
+        <v>47.01935648371725</v>
       </c>
       <c r="O2" t="n">
-        <v>6.78686440289678</v>
+        <v>6.857066171747014</v>
       </c>
       <c r="P2" t="n">
-        <v>373.7984872850384</v>
+        <v>373.9574483484197</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30518,28 +30628,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3109280555248221</v>
+        <v>-0.3213317649552563</v>
       </c>
       <c r="J3" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K3" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09216799815728316</v>
+        <v>0.09722307916191264</v>
       </c>
       <c r="M3" t="n">
-        <v>5.299142704941423</v>
+        <v>5.330062463931907</v>
       </c>
       <c r="N3" t="n">
-        <v>45.87302869143912</v>
+        <v>46.37085356979539</v>
       </c>
       <c r="O3" t="n">
-        <v>6.772963065855233</v>
+        <v>6.809614788649603</v>
       </c>
       <c r="P3" t="n">
-        <v>373.759860342057</v>
+        <v>373.8823427415132</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30596,28 +30706,28 @@
         <v>0.1015</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3563776234528426</v>
+        <v>-0.3668436472358039</v>
       </c>
       <c r="J4" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K4" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1280814541621599</v>
+        <v>0.1336979840770893</v>
       </c>
       <c r="M4" t="n">
-        <v>4.863035190671979</v>
+        <v>4.894982369652152</v>
       </c>
       <c r="N4" t="n">
-        <v>41.65074560135088</v>
+        <v>42.17287088337849</v>
       </c>
       <c r="O4" t="n">
-        <v>6.45373888543307</v>
+        <v>6.494064280816636</v>
       </c>
       <c r="P4" t="n">
-        <v>371.1534348173146</v>
+        <v>371.276651385486</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30674,28 +30784,28 @@
         <v>0.0692</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3777715822873259</v>
+        <v>-0.385327650632336</v>
       </c>
       <c r="J5" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K5" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1695252325975223</v>
+        <v>0.1747720175900913</v>
       </c>
       <c r="M5" t="n">
-        <v>4.38692313680722</v>
+        <v>4.40472217307167</v>
       </c>
       <c r="N5" t="n">
-        <v>33.67928965564251</v>
+        <v>33.90697843953657</v>
       </c>
       <c r="O5" t="n">
-        <v>5.803386050888094</v>
+        <v>5.822969898560061</v>
       </c>
       <c r="P5" t="n">
-        <v>370.8561763308503</v>
+        <v>370.9451354067162</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30752,28 +30862,28 @@
         <v>0.0794</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3652345852743584</v>
+        <v>-0.3740220124624487</v>
       </c>
       <c r="J6" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K6" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1530221781910333</v>
+        <v>0.1585220611695017</v>
       </c>
       <c r="M6" t="n">
-        <v>4.596877178731506</v>
+        <v>4.614662686556893</v>
       </c>
       <c r="N6" t="n">
-        <v>35.56916826242754</v>
+        <v>35.91484894088369</v>
       </c>
       <c r="O6" t="n">
-        <v>5.963989290938368</v>
+        <v>5.992899877428597</v>
       </c>
       <c r="P6" t="n">
-        <v>368.5232889495704</v>
+        <v>368.6267448847577</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30830,28 +30940,28 @@
         <v>0.134</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3183890877751622</v>
+        <v>-0.324860869564379</v>
       </c>
       <c r="J7" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K7" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1280019059646177</v>
+        <v>0.1325546329643773</v>
       </c>
       <c r="M7" t="n">
-        <v>4.621464301039652</v>
+        <v>4.634268632384908</v>
       </c>
       <c r="N7" t="n">
-        <v>33.26807780222688</v>
+        <v>33.40171146539842</v>
       </c>
       <c r="O7" t="n">
-        <v>5.767848628581273</v>
+        <v>5.77942137807916</v>
       </c>
       <c r="P7" t="n">
-        <v>366.0570508237743</v>
+        <v>366.133242699141</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30908,28 +31018,28 @@
         <v>0.1151</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3395391109307211</v>
+        <v>-0.3459588289350614</v>
       </c>
       <c r="J8" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K8" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1430822422467278</v>
+        <v>0.1477424715170707</v>
       </c>
       <c r="M8" t="n">
-        <v>4.580728237357711</v>
+        <v>4.592652517869031</v>
       </c>
       <c r="N8" t="n">
-        <v>33.26176413243568</v>
+        <v>33.39189130521068</v>
       </c>
       <c r="O8" t="n">
-        <v>5.767301286774923</v>
+        <v>5.778571735750165</v>
       </c>
       <c r="P8" t="n">
-        <v>366.619731306878</v>
+        <v>366.6953116929931</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30986,28 +31096,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2145367915736632</v>
+        <v>-0.2204977863552859</v>
       </c>
       <c r="J9" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K9" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06294299870343867</v>
+        <v>0.06631916985435404</v>
       </c>
       <c r="M9" t="n">
-        <v>4.597006704663483</v>
+        <v>4.614530044231002</v>
       </c>
       <c r="N9" t="n">
-        <v>33.00915470086767</v>
+        <v>33.10507097968841</v>
       </c>
       <c r="O9" t="n">
-        <v>5.745359405717598</v>
+        <v>5.753700633478284</v>
       </c>
       <c r="P9" t="n">
-        <v>365.7421628929133</v>
+        <v>365.8123428785517</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31064,28 +31174,28 @@
         <v>0.1027</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08530385274893434</v>
+        <v>-0.09187341434878475</v>
       </c>
       <c r="J10" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K10" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01033101613842724</v>
+        <v>0.0119609518590591</v>
       </c>
       <c r="M10" t="n">
-        <v>4.632948533887136</v>
+        <v>4.647904822117941</v>
       </c>
       <c r="N10" t="n">
-        <v>33.58122021460218</v>
+        <v>33.72211261232101</v>
       </c>
       <c r="O10" t="n">
-        <v>5.794930561672174</v>
+        <v>5.807074359117594</v>
       </c>
       <c r="P10" t="n">
-        <v>364.6136068103785</v>
+        <v>364.6909511604463</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31142,28 +31252,28 @@
         <v>0.0915</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0287206380490653</v>
+        <v>0.02205710865783848</v>
       </c>
       <c r="J11" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K11" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001209270948579366</v>
+        <v>0.0007131261449296877</v>
       </c>
       <c r="M11" t="n">
-        <v>4.565843191579569</v>
+        <v>4.584077950571444</v>
       </c>
       <c r="N11" t="n">
-        <v>32.82096231901593</v>
+        <v>32.97218165616314</v>
       </c>
       <c r="O11" t="n">
-        <v>5.728958222837371</v>
+        <v>5.742140860007106</v>
       </c>
       <c r="P11" t="n">
-        <v>364.86275539425</v>
+        <v>364.9412055774816</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31220,28 +31330,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05535807929620193</v>
+        <v>0.05103205938318128</v>
       </c>
       <c r="J12" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K12" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004707654344578094</v>
+        <v>0.004019043695903557</v>
       </c>
       <c r="M12" t="n">
-        <v>4.552609843906516</v>
+        <v>4.559574920635872</v>
       </c>
       <c r="N12" t="n">
-        <v>31.21191267972418</v>
+        <v>31.21340809398695</v>
       </c>
       <c r="O12" t="n">
-        <v>5.586762271631413</v>
+        <v>5.586896105530061</v>
       </c>
       <c r="P12" t="n">
-        <v>368.0504867546825</v>
+        <v>368.1014204244318</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31279,7 +31389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M525"/>
+  <dimension ref="A1:M527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66457,6 +66567,140 @@
         </is>
       </c>
     </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-45.76012040915242,170.67813054351691</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-45.76037277231855,170.67894526620503</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>-45.76062641204486,170.67975771594263</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>-45.7608516360833,170.68058685664602</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>-45.76107289283466,170.68140635106408</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>-45.76122011539014,170.6822761960433</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>-45.761375480552594,170.68314282633952</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>-45.761472275474624,170.68401922937844</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>-45.76153003165919,170.68490206992956</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>-45.76154421771739,170.68579163512987</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>-45.761488947086654,170.68668865031873</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-45.760127572065976,170.67812487802385</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-45.76037423285025,170.67894426657475</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>-45.76063036762176,170.67975523979746</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>-45.76086104392132,170.6805813501053</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>-45.7610833552509,170.68140160805382</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>-45.76122054808524,170.68227602021656</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>-45.761382801849265,170.68314014747048</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>-45.761480243003504,170.68401716556576</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>-45.76153691622118,170.68490096590264</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>-45.76154888641147,170.6857912023294</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>-45.76150728500091,170.68668754701636</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0500/nzd0500.xlsx
+++ b/data/nzd0500/nzd0500.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M527"/>
+  <dimension ref="A1:M528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24165,6 +24165,51 @@
       <c r="M527" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>346.94</v>
+      </c>
+      <c r="C528" t="n">
+        <v>352.41</v>
+      </c>
+      <c r="D528" t="n">
+        <v>348.56</v>
+      </c>
+      <c r="E528" t="n">
+        <v>350.38</v>
+      </c>
+      <c r="F528" t="n">
+        <v>346.27</v>
+      </c>
+      <c r="G528" t="n">
+        <v>348.07</v>
+      </c>
+      <c r="H528" t="n">
+        <v>347.74</v>
+      </c>
+      <c r="I528" t="n">
+        <v>350.83</v>
+      </c>
+      <c r="J528" t="n">
+        <v>353.33</v>
+      </c>
+      <c r="K528" t="n">
+        <v>358.03</v>
+      </c>
+      <c r="L528" t="n">
+        <v>362.55</v>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -24179,7 +24224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B620"/>
+  <dimension ref="A1:B621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30382,6 +30427,16 @@
       </c>
       <c r="B620" t="n">
         <v>-0.88</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -30550,28 +30605,28 @@
         <v>0.0761</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3628810790515301</v>
+        <v>-0.3696421111590384</v>
       </c>
       <c r="J2" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K2" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1192918267770201</v>
+        <v>0.1223491041542744</v>
       </c>
       <c r="M2" t="n">
-        <v>5.330378007497241</v>
+        <v>5.361036200258613</v>
       </c>
       <c r="N2" t="n">
-        <v>47.01935648371725</v>
+        <v>47.49810482276649</v>
       </c>
       <c r="O2" t="n">
-        <v>6.857066171747014</v>
+        <v>6.891886884066401</v>
       </c>
       <c r="P2" t="n">
-        <v>373.9574483484197</v>
+        <v>374.0372950024032</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30628,28 +30683,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3213317649552563</v>
+        <v>-0.3263656794223909</v>
       </c>
       <c r="J3" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K3" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09722307916191264</v>
+        <v>0.0997266227818483</v>
       </c>
       <c r="M3" t="n">
-        <v>5.330062463931907</v>
+        <v>5.3448746743622</v>
       </c>
       <c r="N3" t="n">
-        <v>46.37085356979539</v>
+        <v>46.59771819335661</v>
       </c>
       <c r="O3" t="n">
-        <v>6.809614788649603</v>
+        <v>6.826252133737561</v>
       </c>
       <c r="P3" t="n">
-        <v>373.8823427415132</v>
+        <v>373.9417924261543</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30706,28 +30761,28 @@
         <v>0.1015</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3668436472358039</v>
+        <v>-0.3718901393213365</v>
       </c>
       <c r="J4" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K4" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1336979840770893</v>
+        <v>0.136470295945027</v>
       </c>
       <c r="M4" t="n">
-        <v>4.894982369652152</v>
+        <v>4.910518256869727</v>
       </c>
       <c r="N4" t="n">
-        <v>42.17287088337849</v>
+        <v>42.40927666173994</v>
       </c>
       <c r="O4" t="n">
-        <v>6.494064280816636</v>
+        <v>6.512240525482758</v>
       </c>
       <c r="P4" t="n">
-        <v>371.276651385486</v>
+        <v>371.3362496096885</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30784,28 +30839,28 @@
         <v>0.0692</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.385327650632336</v>
+        <v>-0.3893410466216379</v>
       </c>
       <c r="J5" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K5" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1747720175900913</v>
+        <v>0.1774883645105629</v>
       </c>
       <c r="M5" t="n">
-        <v>4.40472217307167</v>
+        <v>4.414734599358764</v>
       </c>
       <c r="N5" t="n">
-        <v>33.90697843953657</v>
+        <v>34.04277369005288</v>
       </c>
       <c r="O5" t="n">
-        <v>5.822969898560061</v>
+        <v>5.834618555660077</v>
       </c>
       <c r="P5" t="n">
-        <v>370.9451354067162</v>
+        <v>370.9925329394835</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30862,28 +30917,28 @@
         <v>0.0794</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3740220124624487</v>
+        <v>-0.3788542592186878</v>
       </c>
       <c r="J6" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K6" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1585220611695017</v>
+        <v>0.1614118394277511</v>
       </c>
       <c r="M6" t="n">
-        <v>4.614662686556893</v>
+        <v>4.625289746643472</v>
       </c>
       <c r="N6" t="n">
-        <v>35.91484894088369</v>
+        <v>36.13683219699478</v>
       </c>
       <c r="O6" t="n">
-        <v>5.992899877428597</v>
+        <v>6.011391868527187</v>
       </c>
       <c r="P6" t="n">
-        <v>368.6267448847577</v>
+        <v>368.683812907594</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30940,28 +30995,28 @@
         <v>0.134</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.324860869564379</v>
+        <v>-0.3285292796915358</v>
       </c>
       <c r="J7" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K7" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1325546329643773</v>
+        <v>0.1350285854674315</v>
       </c>
       <c r="M7" t="n">
-        <v>4.634268632384908</v>
+        <v>4.642708722314242</v>
       </c>
       <c r="N7" t="n">
-        <v>33.40171146539842</v>
+        <v>33.50553762684109</v>
       </c>
       <c r="O7" t="n">
-        <v>5.77942137807916</v>
+        <v>5.788396809725564</v>
       </c>
       <c r="P7" t="n">
-        <v>366.133242699141</v>
+        <v>366.176566006801</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31018,28 +31073,28 @@
         <v>0.1151</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3459588289350614</v>
+        <v>-0.3497559083078187</v>
       </c>
       <c r="J8" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K8" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1477424715170707</v>
+        <v>0.1503249678189481</v>
       </c>
       <c r="M8" t="n">
-        <v>4.592652517869031</v>
+        <v>4.601333008747446</v>
       </c>
       <c r="N8" t="n">
-        <v>33.39189130521068</v>
+        <v>33.50767135781954</v>
       </c>
       <c r="O8" t="n">
-        <v>5.778571735750165</v>
+        <v>5.788581117840497</v>
       </c>
       <c r="P8" t="n">
-        <v>366.6953116929931</v>
+        <v>366.7401545628395</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31096,28 +31151,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2204977863552859</v>
+        <v>-0.224046239640867</v>
       </c>
       <c r="J9" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K9" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06631916985435404</v>
+        <v>0.06827099041269347</v>
       </c>
       <c r="M9" t="n">
-        <v>4.614530044231002</v>
+        <v>4.626593025723729</v>
       </c>
       <c r="N9" t="n">
-        <v>33.10507097968841</v>
+        <v>33.19870349506464</v>
       </c>
       <c r="O9" t="n">
-        <v>5.753700633478284</v>
+        <v>5.761831609398581</v>
       </c>
       <c r="P9" t="n">
-        <v>365.8123428785517</v>
+        <v>365.8542495160539</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31174,28 +31229,28 @@
         <v>0.1027</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09187341434878475</v>
+        <v>-0.09534751712351258</v>
       </c>
       <c r="J10" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K10" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0119609518590591</v>
+        <v>0.0128637524194366</v>
       </c>
       <c r="M10" t="n">
-        <v>4.647904822117941</v>
+        <v>4.656719157092363</v>
       </c>
       <c r="N10" t="n">
-        <v>33.72211261232101</v>
+        <v>33.80808676271226</v>
       </c>
       <c r="O10" t="n">
-        <v>5.807074359117594</v>
+        <v>5.814472182641539</v>
       </c>
       <c r="P10" t="n">
-        <v>364.6909511604463</v>
+        <v>364.7319797308992</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31252,28 +31307,28 @@
         <v>0.0915</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02205710865783848</v>
+        <v>0.01913630159664407</v>
       </c>
       <c r="J11" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K11" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0007131261449296877</v>
+        <v>0.000537224277610604</v>
       </c>
       <c r="M11" t="n">
-        <v>4.584077950571444</v>
+        <v>4.591036182545826</v>
       </c>
       <c r="N11" t="n">
-        <v>32.97218165616314</v>
+        <v>33.01561550706741</v>
       </c>
       <c r="O11" t="n">
-        <v>5.742140860007106</v>
+        <v>5.745921641222355</v>
       </c>
       <c r="P11" t="n">
-        <v>364.9412055774816</v>
+        <v>364.9756998184583</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31330,28 +31385,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05103205938318128</v>
+        <v>0.04833764891337989</v>
       </c>
       <c r="J12" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K12" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004019043695903557</v>
+        <v>0.003610941263864076</v>
       </c>
       <c r="M12" t="n">
-        <v>4.559574920635872</v>
+        <v>4.565919583927103</v>
       </c>
       <c r="N12" t="n">
-        <v>31.21340809398695</v>
+        <v>31.24438370972211</v>
       </c>
       <c r="O12" t="n">
-        <v>5.586896105530061</v>
+        <v>5.589667584903606</v>
       </c>
       <c r="P12" t="n">
-        <v>368.1014204244318</v>
+        <v>368.1332409596771</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31389,7 +31444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M527"/>
+  <dimension ref="A1:M528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66701,6 +66756,73 @@
         </is>
       </c>
     </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>-45.760125761659275,170.6781263099618</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>-45.760371230646165,170.6789463213703</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>-45.76062575278203,170.67975812863344</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-45.76086245925974,170.6805805216875</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>-45.761088929488956,170.68139908103942</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>-45.76123084622843,170.68227183553947</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>-45.76139317368605,170.68313635240474</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>-45.761489981094286,170.68401464312717</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>-45.7615386150092,170.68490069348036</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>-45.76153784315434,170.68579222606886</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>-45.76151079077864,170.6866873360908</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0500/nzd0500.xlsx
+++ b/data/nzd0500/nzd0500.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M528"/>
+  <dimension ref="A1:M535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24210,6 +24210,321 @@
       <c r="M528" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>346.93</v>
+      </c>
+      <c r="C529" t="n">
+        <v>351.31</v>
+      </c>
+      <c r="D529" t="n">
+        <v>347.46</v>
+      </c>
+      <c r="E529" t="n">
+        <v>350.99</v>
+      </c>
+      <c r="F529" t="n">
+        <v>347.36</v>
+      </c>
+      <c r="G529" t="n">
+        <v>347.89</v>
+      </c>
+      <c r="H529" t="n">
+        <v>347.14</v>
+      </c>
+      <c r="I529" t="n">
+        <v>349.95</v>
+      </c>
+      <c r="J529" t="n">
+        <v>353.51</v>
+      </c>
+      <c r="K529" t="n">
+        <v>357.9</v>
+      </c>
+      <c r="L529" t="n">
+        <v>362.12</v>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>345.71</v>
+      </c>
+      <c r="C530" t="n">
+        <v>349.31</v>
+      </c>
+      <c r="D530" t="n">
+        <v>347.39</v>
+      </c>
+      <c r="E530" t="n">
+        <v>350.85</v>
+      </c>
+      <c r="F530" t="n">
+        <v>349.75</v>
+      </c>
+      <c r="G530" t="n">
+        <v>348.69</v>
+      </c>
+      <c r="H530" t="n">
+        <v>348.64</v>
+      </c>
+      <c r="I530" t="n">
+        <v>350.87</v>
+      </c>
+      <c r="J530" t="n">
+        <v>353.4</v>
+      </c>
+      <c r="K530" t="n">
+        <v>357.52</v>
+      </c>
+      <c r="L530" t="n">
+        <v>359.47</v>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>347.23</v>
+      </c>
+      <c r="C531" t="n">
+        <v>350.97</v>
+      </c>
+      <c r="D531" t="n">
+        <v>349.38</v>
+      </c>
+      <c r="E531" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="F531" t="n">
+        <v>351.49</v>
+      </c>
+      <c r="G531" t="n">
+        <v>350.78</v>
+      </c>
+      <c r="H531" t="n">
+        <v>350.05</v>
+      </c>
+      <c r="I531" t="n">
+        <v>352.67</v>
+      </c>
+      <c r="J531" t="n">
+        <v>355.4</v>
+      </c>
+      <c r="K531" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="L531" t="n">
+        <v>360.98</v>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>347.01</v>
+      </c>
+      <c r="C532" t="n">
+        <v>350.17</v>
+      </c>
+      <c r="D532" t="n">
+        <v>348.23</v>
+      </c>
+      <c r="E532" t="n">
+        <v>351.53</v>
+      </c>
+      <c r="F532" t="n">
+        <v>351.18</v>
+      </c>
+      <c r="G532" t="n">
+        <v>349.88</v>
+      </c>
+      <c r="H532" t="n">
+        <v>349.19</v>
+      </c>
+      <c r="I532" t="n">
+        <v>351.6</v>
+      </c>
+      <c r="J532" t="n">
+        <v>355.28</v>
+      </c>
+      <c r="K532" t="n">
+        <v>359.22</v>
+      </c>
+      <c r="L532" t="n">
+        <v>360.98</v>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>348.45</v>
+      </c>
+      <c r="C533" t="n">
+        <v>351.82</v>
+      </c>
+      <c r="D533" t="n">
+        <v>349.6</v>
+      </c>
+      <c r="E533" t="n">
+        <v>352.67</v>
+      </c>
+      <c r="F533" t="n">
+        <v>352.6</v>
+      </c>
+      <c r="G533" t="n">
+        <v>351.55</v>
+      </c>
+      <c r="H533" t="n">
+        <v>350.47</v>
+      </c>
+      <c r="I533" t="n">
+        <v>353.16</v>
+      </c>
+      <c r="J533" t="n">
+        <v>357.05</v>
+      </c>
+      <c r="K533" t="n">
+        <v>360.88</v>
+      </c>
+      <c r="L533" t="n">
+        <v>362.41</v>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>350.63</v>
+      </c>
+      <c r="C534" t="n">
+        <v>352.99</v>
+      </c>
+      <c r="D534" t="n">
+        <v>350.33</v>
+      </c>
+      <c r="E534" t="n">
+        <v>353.23</v>
+      </c>
+      <c r="F534" t="n">
+        <v>353.25</v>
+      </c>
+      <c r="G534" t="n">
+        <v>352.75</v>
+      </c>
+      <c r="H534" t="n">
+        <v>351.23</v>
+      </c>
+      <c r="I534" t="n">
+        <v>354.17</v>
+      </c>
+      <c r="J534" t="n">
+        <v>358.37</v>
+      </c>
+      <c r="K534" t="n">
+        <v>361.96</v>
+      </c>
+      <c r="L534" t="n">
+        <v>364.07</v>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>350.64</v>
+      </c>
+      <c r="C535" t="n">
+        <v>352.04</v>
+      </c>
+      <c r="D535" t="n">
+        <v>348.96</v>
+      </c>
+      <c r="E535" t="n">
+        <v>352.86</v>
+      </c>
+      <c r="F535" t="n">
+        <v>353.76</v>
+      </c>
+      <c r="G535" t="n">
+        <v>352.66</v>
+      </c>
+      <c r="H535" t="n">
+        <v>350.98</v>
+      </c>
+      <c r="I535" t="n">
+        <v>353.86</v>
+      </c>
+      <c r="J535" t="n">
+        <v>358.22</v>
+      </c>
+      <c r="K535" t="n">
+        <v>361.8</v>
+      </c>
+      <c r="L535" t="n">
+        <v>364.73</v>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -24224,7 +24539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B621"/>
+  <dimension ref="A1:B628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30437,6 +30752,76 @@
       </c>
       <c r="B621" t="n">
         <v>0.25</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -30605,28 +30990,28 @@
         <v>0.0761</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3696421111590384</v>
+        <v>-0.4120667269239827</v>
       </c>
       <c r="J2" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K2" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1223491041542744</v>
+        <v>0.1425452567266839</v>
       </c>
       <c r="M2" t="n">
-        <v>5.361036200258613</v>
+        <v>5.55218732357616</v>
       </c>
       <c r="N2" t="n">
-        <v>47.49810482276649</v>
+        <v>50.17529987250664</v>
       </c>
       <c r="O2" t="n">
-        <v>6.891886884066401</v>
+        <v>7.083452539017018</v>
       </c>
       <c r="P2" t="n">
-        <v>374.0372950024032</v>
+        <v>374.5396533494937</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30683,28 +31068,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3263656794223909</v>
+        <v>-0.3632951419570983</v>
       </c>
       <c r="J3" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K3" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0997266227818483</v>
+        <v>0.1179787374262282</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3448746743622</v>
+        <v>5.45971208726265</v>
       </c>
       <c r="N3" t="n">
-        <v>46.59771819335661</v>
+        <v>48.47199954060037</v>
       </c>
       <c r="O3" t="n">
-        <v>6.826252133737561</v>
+        <v>6.962183532527735</v>
       </c>
       <c r="P3" t="n">
-        <v>373.9417924261543</v>
+        <v>374.3791052315561</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30761,28 +31146,28 @@
         <v>0.1015</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3718901393213365</v>
+        <v>-0.4052416884176179</v>
       </c>
       <c r="J4" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K4" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="L4" t="n">
-        <v>0.136470295945027</v>
+        <v>0.155294781301358</v>
       </c>
       <c r="M4" t="n">
-        <v>4.910518256869727</v>
+        <v>5.009172044898754</v>
       </c>
       <c r="N4" t="n">
-        <v>42.40927666173994</v>
+        <v>43.8806439435688</v>
       </c>
       <c r="O4" t="n">
-        <v>6.512240525482758</v>
+        <v>6.624246669891513</v>
       </c>
       <c r="P4" t="n">
-        <v>371.3362496096885</v>
+        <v>371.7311901074567</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30839,28 +31224,28 @@
         <v>0.0692</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3893410466216379</v>
+        <v>-0.4117793144020568</v>
       </c>
       <c r="J5" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K5" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1774883645105629</v>
+        <v>0.1943997317552638</v>
       </c>
       <c r="M5" t="n">
-        <v>4.414734599358764</v>
+        <v>4.461085406255794</v>
       </c>
       <c r="N5" t="n">
-        <v>34.04277369005288</v>
+        <v>34.51830304598762</v>
       </c>
       <c r="O5" t="n">
-        <v>5.834618555660077</v>
+        <v>5.875227914386608</v>
       </c>
       <c r="P5" t="n">
-        <v>370.9925329394835</v>
+        <v>371.2582323605162</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30917,28 +31302,28 @@
         <v>0.0794</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3788542592186878</v>
+        <v>-0.3979097394732148</v>
       </c>
       <c r="J6" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K6" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1614118394277511</v>
+        <v>0.176151511964144</v>
       </c>
       <c r="M6" t="n">
-        <v>4.625289746643472</v>
+        <v>4.640433691943741</v>
       </c>
       <c r="N6" t="n">
-        <v>36.13683219699478</v>
+        <v>36.3769728922919</v>
       </c>
       <c r="O6" t="n">
-        <v>6.011391868527187</v>
+        <v>6.031332596722875</v>
       </c>
       <c r="P6" t="n">
-        <v>368.683812907594</v>
+        <v>368.9094064304197</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30995,28 +31380,28 @@
         <v>0.134</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3285292796915358</v>
+        <v>-0.34647301184107</v>
       </c>
       <c r="J7" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K7" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1350285854674315</v>
+        <v>0.1489642042948462</v>
       </c>
       <c r="M7" t="n">
-        <v>4.642708722314242</v>
+        <v>4.666823688915546</v>
       </c>
       <c r="N7" t="n">
-        <v>33.50553762684109</v>
+        <v>33.69001257170322</v>
       </c>
       <c r="O7" t="n">
-        <v>5.788396809725564</v>
+        <v>5.804309827335479</v>
       </c>
       <c r="P7" t="n">
-        <v>366.176566006801</v>
+        <v>366.3890057837156</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31073,28 +31458,28 @@
         <v>0.1151</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3497559083078187</v>
+        <v>-0.3701373236975069</v>
       </c>
       <c r="J8" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K8" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1503249678189481</v>
+        <v>0.1658695812206143</v>
       </c>
       <c r="M8" t="n">
-        <v>4.601333008747446</v>
+        <v>4.633910112453919</v>
       </c>
       <c r="N8" t="n">
-        <v>33.50767135781954</v>
+        <v>33.84460235747964</v>
       </c>
       <c r="O8" t="n">
-        <v>5.788581117840497</v>
+        <v>5.817611396224368</v>
       </c>
       <c r="P8" t="n">
-        <v>366.7401545628395</v>
+        <v>366.9814779173468</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31151,28 +31536,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.224046239640867</v>
+        <v>-0.2439493592613483</v>
       </c>
       <c r="J9" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K9" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06827099041269347</v>
+        <v>0.08024294785561481</v>
       </c>
       <c r="M9" t="n">
-        <v>4.626593025723729</v>
+        <v>4.683712825989987</v>
       </c>
       <c r="N9" t="n">
-        <v>33.19870349506464</v>
+        <v>33.50904564997391</v>
       </c>
       <c r="O9" t="n">
-        <v>5.761831609398581</v>
+        <v>5.788699823792378</v>
       </c>
       <c r="P9" t="n">
-        <v>365.8542495160539</v>
+        <v>366.0899048262253</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31229,28 +31614,28 @@
         <v>0.1027</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09534751712351258</v>
+        <v>-0.1119477032570781</v>
       </c>
       <c r="J10" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K10" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0128637524194366</v>
+        <v>0.01783037145623634</v>
       </c>
       <c r="M10" t="n">
-        <v>4.656719157092363</v>
+        <v>4.680935192417842</v>
       </c>
       <c r="N10" t="n">
-        <v>33.80808676271226</v>
+        <v>33.91196297724206</v>
       </c>
       <c r="O10" t="n">
-        <v>5.814472182641539</v>
+        <v>5.82339788931188</v>
       </c>
       <c r="P10" t="n">
-        <v>364.7319797308992</v>
+        <v>364.9285018056011</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31307,28 +31692,28 @@
         <v>0.0915</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01913630159664407</v>
+        <v>0.004211669813066065</v>
       </c>
       <c r="J11" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K11" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="L11" t="n">
-        <v>0.000537224277610604</v>
+        <v>2.638701428780976e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.591036182545826</v>
+        <v>4.610563700867129</v>
       </c>
       <c r="N11" t="n">
-        <v>33.01561550706741</v>
+        <v>33.02199930084134</v>
       </c>
       <c r="O11" t="n">
-        <v>5.745921641222355</v>
+        <v>5.746477120883832</v>
       </c>
       <c r="P11" t="n">
-        <v>364.9756998184583</v>
+        <v>365.1523892197055</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31385,28 +31770,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>0.04833764891337989</v>
+        <v>0.02904437434195708</v>
       </c>
       <c r="J12" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="K12" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003610941263864076</v>
+        <v>0.001311873256415241</v>
       </c>
       <c r="M12" t="n">
-        <v>4.565919583927103</v>
+        <v>4.613267955342994</v>
       </c>
       <c r="N12" t="n">
-        <v>31.24438370972211</v>
+        <v>31.54703176605104</v>
       </c>
       <c r="O12" t="n">
-        <v>5.589667584903606</v>
+        <v>5.616674440098077</v>
       </c>
       <c r="P12" t="n">
-        <v>368.1332409596771</v>
+        <v>368.3616756448806</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31444,7 +31829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M528"/>
+  <dimension ref="A1:M535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66823,6 +67208,475 @@
         </is>
       </c>
     </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>-45.76012584037262,170.67812624770363</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>-45.76038015611767,170.67894021251803</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>-45.76063481764569,170.67975245413373</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>-45.76085738069239,170.68058349424527</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>-45.76107958192049,170.6814033186479</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>-45.76123240393075,170.68227120256296</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>-45.761398403183534,170.68313443892566</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>-45.76149777156684,170.68401262517563</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>-45.761537005631084,170.68490095156463</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>-45.76153901032786,170.68579211786877</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>-45.76151465612329,170.68668710353182</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>-45.760135443399186,170.67811865220557</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>-45.76039638424672,170.67892910550884</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>-45.76063539450064,170.67975209302912</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>-45.760858546265226,170.68058281201894</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>-45.761059085875154,170.6814126102797</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>-45.76122548080932,170.6822740157916</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>-45.76138532943976,170.68313922262266</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>-45.761489626981884,170.68401473485224</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>-45.761537989139946,170.68490079384648</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>-45.76154242206584,170.68579180159156</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>-45.76153847743334,170.68668567031847</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>-45.76012347897256,170.67812811544863</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>-45.7603829148997,170.67893832432694</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>-45.76061899533802,170.67976235871384</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>-45.760844809156424,170.6805908525416</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>-45.761044164067506,170.6814193748942</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>-45.761207394154155,170.68228136534796</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>-45.76137304012035,170.6831437192957</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>-45.7614736919242,170.68401886247844</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>-45.761520107160706,170.68490366144837</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>-45.761524645115294,170.68579344956174</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>-45.761524903781215,170.68668648697985</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>-45.76012521066593,170.67812674576896</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>-45.76038940615138,170.6789338815236</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>-45.76062847224118,170.67975642628375</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>-45.76085288491139,170.6805861256894</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>-45.76104682255052,170.68141816970453</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>-45.76121518266603,170.68227820046783</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>-45.76138053573363,170.68314097664432</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>-45.76148316443075,170.68401640883428</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>-45.76152118007945,170.68490348939233</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>-45.761527159027494,170.68579321651552</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>-45.761524903781215,170.68668648697985</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>-45.76011387594527,170.6781357109434</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>-45.760376017944566,170.67894304480433</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>-45.7606171823652,170.67976349361328</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>-45.76084339381791,170.68059168095886</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>-45.761034644983035,170.68142369024977</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>-45.76120073064946,170.68228407307802</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>-45.76136937947198,170.68314505872982</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>-45.761469354047364,170.6840199861096</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>-45.76150535452771,170.6849060272184</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>-45.761512255119406,170.68579459814623</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>-45.76151204926293,170.68668726037393</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>-45.76009671643609,170.6781492832143</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>-45.76036652448831,170.67894954240066</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>-45.76061116659165,170.67976725941543</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>-45.76083873152625,170.68059440986246</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>-45.76102907074429,170.6814262172591</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>-45.76119034596665,170.68228829291567</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>-45.76136275544151,170.6831474824673</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>-45.76146041270929,170.68402230216506</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>-45.76149355242125,170.68490791983342</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>-45.76150255860086,170.68579549703804</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>-45.76149712723468,170.68668815815946</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>-45.760096637722725,170.67814934547238</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>-45.76037423285025,170.67894426657475</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>-45.76062245646791,170.67976019208743</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>-45.76084181196894,170.68059260683694</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>-45.76102469711077,170.6814281999891</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>-45.761191124817884,170.68228797642792</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>-45.76136493439892,170.6831466851853</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>-45.761463157080385,170.68402159129664</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>-45.76149489356971,170.6849077047636</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>-45.76150399512212,170.6857953638689</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>-45.76149119438007,170.68668851511018</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0500/nzd0500.xlsx
+++ b/data/nzd0500/nzd0500.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M535"/>
+  <dimension ref="A1:M540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24523,6 +24523,231 @@
         <v>364.73</v>
       </c>
       <c r="M535" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>352.09</v>
+      </c>
+      <c r="C536" t="n">
+        <v>351.97</v>
+      </c>
+      <c r="D536" t="n">
+        <v>349.15</v>
+      </c>
+      <c r="E536" t="n">
+        <v>353.49</v>
+      </c>
+      <c r="F536" t="n">
+        <v>354.4</v>
+      </c>
+      <c r="G536" t="n">
+        <v>352.12</v>
+      </c>
+      <c r="H536" t="n">
+        <v>350.81</v>
+      </c>
+      <c r="I536" t="n">
+        <v>353.53</v>
+      </c>
+      <c r="J536" t="n">
+        <v>360.12</v>
+      </c>
+      <c r="K536" t="n">
+        <v>363.79</v>
+      </c>
+      <c r="L536" t="n">
+        <v>366.31</v>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>352.71</v>
+      </c>
+      <c r="C537" t="n">
+        <v>352.79</v>
+      </c>
+      <c r="D537" t="n">
+        <v>349.71</v>
+      </c>
+      <c r="E537" t="n">
+        <v>354.29</v>
+      </c>
+      <c r="F537" t="n">
+        <v>355.25</v>
+      </c>
+      <c r="G537" t="n">
+        <v>352.58</v>
+      </c>
+      <c r="H537" t="n">
+        <v>351.95</v>
+      </c>
+      <c r="I537" t="n">
+        <v>354.21</v>
+      </c>
+      <c r="J537" t="n">
+        <v>361.39</v>
+      </c>
+      <c r="K537" t="n">
+        <v>364.6</v>
+      </c>
+      <c r="L537" t="n">
+        <v>367.96</v>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>353.05</v>
+      </c>
+      <c r="C538" t="n">
+        <v>353.09</v>
+      </c>
+      <c r="D538" t="n">
+        <v>350.34</v>
+      </c>
+      <c r="E538" t="n">
+        <v>354.81</v>
+      </c>
+      <c r="F538" t="n">
+        <v>355.31</v>
+      </c>
+      <c r="G538" t="n">
+        <v>353.35</v>
+      </c>
+      <c r="H538" t="n">
+        <v>352.32</v>
+      </c>
+      <c r="I538" t="n">
+        <v>354.78</v>
+      </c>
+      <c r="J538" t="n">
+        <v>361.75</v>
+      </c>
+      <c r="K538" t="n">
+        <v>365.32</v>
+      </c>
+      <c r="L538" t="n">
+        <v>368.52</v>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>353.65</v>
+      </c>
+      <c r="C539" t="n">
+        <v>353.88</v>
+      </c>
+      <c r="D539" t="n">
+        <v>351.11</v>
+      </c>
+      <c r="E539" t="n">
+        <v>355.25</v>
+      </c>
+      <c r="F539" t="n">
+        <v>355.38</v>
+      </c>
+      <c r="G539" t="n">
+        <v>354.12</v>
+      </c>
+      <c r="H539" t="n">
+        <v>352.84</v>
+      </c>
+      <c r="I539" t="n">
+        <v>355.51</v>
+      </c>
+      <c r="J539" t="n">
+        <v>362.47</v>
+      </c>
+      <c r="K539" t="n">
+        <v>366.01</v>
+      </c>
+      <c r="L539" t="n">
+        <v>368.86</v>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>353.2</v>
+      </c>
+      <c r="C540" t="n">
+        <v>353.88</v>
+      </c>
+      <c r="D540" t="n">
+        <v>351.11</v>
+      </c>
+      <c r="E540" t="n">
+        <v>355.25</v>
+      </c>
+      <c r="F540" t="n">
+        <v>355.38</v>
+      </c>
+      <c r="G540" t="n">
+        <v>354.12</v>
+      </c>
+      <c r="H540" t="n">
+        <v>352.84</v>
+      </c>
+      <c r="I540" t="n">
+        <v>355.51</v>
+      </c>
+      <c r="J540" t="n">
+        <v>362.47</v>
+      </c>
+      <c r="K540" t="n">
+        <v>366.01</v>
+      </c>
+      <c r="L540" t="n">
+        <v>368.86</v>
+      </c>
+      <c r="M540" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24539,7 +24764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B628"/>
+  <dimension ref="A1:B633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30822,6 +31047,56 @@
       </c>
       <c r="B628" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>0.46</v>
       </c>
     </row>
   </sheetData>
@@ -30990,28 +31265,28 @@
         <v>0.0761</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4120667269239827</v>
+        <v>-0.4316123231377244</v>
       </c>
       <c r="J2" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="K2" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1425452567266839</v>
+        <v>0.1540726296811264</v>
       </c>
       <c r="M2" t="n">
-        <v>5.55218732357616</v>
+        <v>5.621591195464429</v>
       </c>
       <c r="N2" t="n">
-        <v>50.17529987250664</v>
+        <v>50.71730317266314</v>
       </c>
       <c r="O2" t="n">
-        <v>7.083452539017018</v>
+        <v>7.121608187246975</v>
       </c>
       <c r="P2" t="n">
-        <v>374.5396533494937</v>
+        <v>374.772133967087</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31068,28 +31343,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3632951419570983</v>
+        <v>-0.3846283578293235</v>
       </c>
       <c r="J3" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="K3" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1179787374262282</v>
+        <v>0.1296980560845339</v>
       </c>
       <c r="M3" t="n">
-        <v>5.45971208726265</v>
+        <v>5.519854631250619</v>
       </c>
       <c r="N3" t="n">
-        <v>48.47199954060037</v>
+        <v>49.22434962815392</v>
       </c>
       <c r="O3" t="n">
-        <v>6.962183532527735</v>
+        <v>7.016006672470739</v>
       </c>
       <c r="P3" t="n">
-        <v>374.3791052315561</v>
+        <v>374.6328451838249</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31146,28 +31421,28 @@
         <v>0.1015</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4052416884176179</v>
+        <v>-0.4248478263855179</v>
       </c>
       <c r="J4" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="K4" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="L4" t="n">
-        <v>0.155294781301358</v>
+        <v>0.1674776606853076</v>
       </c>
       <c r="M4" t="n">
-        <v>5.009172044898754</v>
+        <v>5.062045156649354</v>
       </c>
       <c r="N4" t="n">
-        <v>43.8806439435688</v>
+        <v>44.49044092450894</v>
       </c>
       <c r="O4" t="n">
-        <v>6.624246669891513</v>
+        <v>6.670115510582177</v>
       </c>
       <c r="P4" t="n">
-        <v>371.7311901074567</v>
+        <v>371.9643860412583</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31224,28 +31499,28 @@
         <v>0.0692</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4117793144020568</v>
+        <v>-0.4221543083576042</v>
       </c>
       <c r="J5" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="K5" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1943997317552638</v>
+        <v>0.2039812561893454</v>
       </c>
       <c r="M5" t="n">
-        <v>4.461085406255794</v>
+        <v>4.468975785664935</v>
       </c>
       <c r="N5" t="n">
-        <v>34.51830304598762</v>
+        <v>34.48548853040494</v>
       </c>
       <c r="O5" t="n">
-        <v>5.875227914386608</v>
+        <v>5.87243463398316</v>
       </c>
       <c r="P5" t="n">
-        <v>371.2582323605162</v>
+        <v>371.381629618267</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31302,28 +31577,28 @@
         <v>0.0794</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3979097394732148</v>
+        <v>-0.4036540777981009</v>
       </c>
       <c r="J6" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="K6" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="L6" t="n">
-        <v>0.176151511964144</v>
+        <v>0.1827628878864491</v>
       </c>
       <c r="M6" t="n">
-        <v>4.640433691943741</v>
+        <v>4.619947308671454</v>
       </c>
       <c r="N6" t="n">
-        <v>36.3769728922919</v>
+        <v>36.12764524453947</v>
       </c>
       <c r="O6" t="n">
-        <v>6.031332596722875</v>
+        <v>6.010627691392927</v>
       </c>
       <c r="P6" t="n">
-        <v>368.9094064304197</v>
+        <v>368.9777290402023</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31380,28 +31655,28 @@
         <v>0.134</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.34647301184107</v>
+        <v>-0.3535874495516651</v>
       </c>
       <c r="J7" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="K7" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1489642042948462</v>
+        <v>0.156093959895704</v>
       </c>
       <c r="M7" t="n">
-        <v>4.666823688915546</v>
+        <v>4.657991574907131</v>
       </c>
       <c r="N7" t="n">
-        <v>33.69001257170322</v>
+        <v>33.51680238640356</v>
       </c>
       <c r="O7" t="n">
-        <v>5.804309827335479</v>
+        <v>5.789369774543993</v>
       </c>
       <c r="P7" t="n">
-        <v>366.3890057837156</v>
+        <v>366.4736177894819</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31458,28 +31733,28 @@
         <v>0.1151</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3701373236975069</v>
+        <v>-0.3792247532341144</v>
       </c>
       <c r="J8" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="K8" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1658695812206143</v>
+        <v>0.1744206627134008</v>
       </c>
       <c r="M8" t="n">
-        <v>4.633910112453919</v>
+        <v>4.63229132702996</v>
       </c>
       <c r="N8" t="n">
-        <v>33.84460235747964</v>
+        <v>33.75321425144472</v>
       </c>
       <c r="O8" t="n">
-        <v>5.817611396224368</v>
+        <v>5.809751651443005</v>
       </c>
       <c r="P8" t="n">
-        <v>366.9814779173468</v>
+        <v>367.0895594835189</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31536,28 +31811,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2439493592613483</v>
+        <v>-0.2529149785797236</v>
       </c>
       <c r="J9" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="K9" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08024294785561481</v>
+        <v>0.08669268806242636</v>
       </c>
       <c r="M9" t="n">
-        <v>4.683712825989987</v>
+        <v>4.693774484622535</v>
       </c>
       <c r="N9" t="n">
-        <v>33.50904564997391</v>
+        <v>33.41523082373804</v>
       </c>
       <c r="O9" t="n">
-        <v>5.788699823792378</v>
+        <v>5.78059087150596</v>
       </c>
       <c r="P9" t="n">
-        <v>366.0899048262253</v>
+        <v>366.1965365905747</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31614,28 +31889,28 @@
         <v>0.1027</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1119477032570781</v>
+        <v>-0.1124786227504435</v>
       </c>
       <c r="J10" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="K10" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01783037145623634</v>
+        <v>0.01832576937148811</v>
       </c>
       <c r="M10" t="n">
-        <v>4.680935192417842</v>
+        <v>4.644359611092201</v>
       </c>
       <c r="N10" t="n">
-        <v>33.91196297724206</v>
+        <v>33.60516659477851</v>
       </c>
       <c r="O10" t="n">
-        <v>5.82339788931188</v>
+        <v>5.796996342484486</v>
       </c>
       <c r="P10" t="n">
-        <v>364.9285018056011</v>
+        <v>364.9348058338977</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31692,28 +31967,28 @@
         <v>0.0915</v>
       </c>
       <c r="I11" t="n">
-        <v>0.004211669813066065</v>
+        <v>0.003989329011720989</v>
       </c>
       <c r="J11" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="K11" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="L11" t="n">
-        <v>2.638701428780976e-05</v>
+        <v>2.41158209022263e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.610563700867129</v>
+        <v>4.574743662370562</v>
       </c>
       <c r="N11" t="n">
-        <v>33.02199930084134</v>
+        <v>32.72262128220069</v>
       </c>
       <c r="O11" t="n">
-        <v>5.746477120883832</v>
+        <v>5.720368981298383</v>
       </c>
       <c r="P11" t="n">
-        <v>365.1523892197055</v>
+        <v>365.155022327489</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31770,28 +32045,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02904437434195708</v>
+        <v>0.02712260266806861</v>
       </c>
       <c r="J12" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="K12" t="n">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001311873256415241</v>
+        <v>0.001165075527816306</v>
       </c>
       <c r="M12" t="n">
-        <v>4.613267955342994</v>
+        <v>4.581102200390484</v>
       </c>
       <c r="N12" t="n">
-        <v>31.54703176605104</v>
+        <v>31.27254754405591</v>
       </c>
       <c r="O12" t="n">
-        <v>5.616674440098077</v>
+        <v>5.592186293754519</v>
       </c>
       <c r="P12" t="n">
-        <v>368.3616756448806</v>
+        <v>368.3845229474786</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31829,7 +32104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M535"/>
+  <dimension ref="A1:M540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67677,6 +67952,341 @@
         </is>
       </c>
     </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>-45.76008522428671,170.67815837289558</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>-45.760374800834825,170.67894387782962</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>-45.76062089071868,170.67976117222798</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>-45.76083656689082,170.68059567685327</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>-45.76101920862943,170.68143068812043</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>-45.761195797925154,170.68228607750112</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>-45.76136641608994,170.6831461430335</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>-45.761466078507674,170.68402083456564</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>-45.76147790568908,170.68491042898074</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>-45.761486128388796,170.68579702015938</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>-45.76147699148564,170.68668936962808</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>-45.76008034405864,170.67816223289606</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>-45.76036814730137,170.6789484317006</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>-45.760616275878775,170.67976406106297</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>-45.76082990647398,170.68059957528584</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>-45.76101191924003,170.6814339926691</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>-45.76119181713008,170.68228769510546</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>-45.76135648004419,170.68314977863906</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>-45.761460058596896,170.68402239389</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>-45.76146655063194,170.68491224990382</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>-45.76147885599984,170.6857976943275</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>-45.761462159348994,170.6866902620038</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>-45.76007766780447,170.67816434967023</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>-45.76036571308178,170.6789500977507</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>-45.76061108418381,170.67976731100174</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>-45.76082557720296,170.68060210926652</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>-45.761011404694884,170.6814342259313</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>-45.76118515362518,170.68229040283393</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>-45.761353255187196,170.68315095861604</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>-45.76145501249517,170.68402370097044</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>-45.76146333187559,170.68491276607082</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>-45.76147239165405,170.68579829358785</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>-45.761457125411695,170.68669056487056</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>-45.7600729450029,170.67816808515354</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>-45.76035930297001,170.67895448501517</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>-45.76060473877865,170.6797712831483</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>-45.760821913973565,170.6806042534037</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>-45.761010804392235,170.68143449807056</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>-45.76117849012021,170.68229311056172</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>-45.761348722955724,170.68315261696176</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>-45.76144854994383,170.68402537495027</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>-45.76145689436283,170.68491379840466</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>-45.76146619665604,170.6857988678789</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>-45.761454069092615,170.68669074875393</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>-45.7600764871041,170.67816528354112</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>-45.76035930297001,170.67895448501517</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>-45.76060473877865,170.6797712831483</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>-45.760821913973565,170.6806042534037</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>-45.761010804392235,170.68143449807056</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>-45.76117849012021,170.68229311056172</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>-45.761348722955724,170.68315261696176</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>-45.76144854994383,170.68402537495027</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>-45.76145689436283,170.68491379840466</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>-45.76146619665604,170.6857988678789</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>-45.761454069092615,170.68669074875393</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
